--- a/output/free_fire_creators.xlsx
+++ b/output/free_fire_creators.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0AE6506-C245-4D04-920D-22D08F70B779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176"/>
   </bookViews>
   <sheets>
-    <sheet name="Free Fire Creators" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Free Fire Creators" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="370">
   <si>
     <t>Name</t>
   </si>
@@ -930,50 +929,245 @@
   </si>
   <si>
     <t>https://www.instagram.com/krupaislive?stkn=ODl4dHIwcm1nNWlz&amp;utm_source=qr</t>
+  </si>
+  <si>
+    <t>BR0KE CODM</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@brokecodm</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/br0kecodm?igsh=MW9xMmJmamloZDlkYQ==</t>
+  </si>
+  <si>
+    <t>NOOB CODM</t>
+  </si>
+  <si>
+    <t>investor.mailbox20@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@NoobCodmLive</t>
+  </si>
+  <si>
+    <t>DarkNyx</t>
+  </si>
+  <si>
+    <t>darknyx@amplifiedim.com</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@DarkNyxMobile</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/darknyxyt/</t>
+  </si>
+  <si>
+    <t>ELLA LIFESTYLE</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@EllaLifestyleTV</t>
+  </si>
+  <si>
+    <t>AyeoRaph</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@AyeoRaph</t>
+  </si>
+  <si>
+    <t>KAME</t>
+  </si>
+  <si>
+    <t>//www.youtube.com/@no.6615</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@kame5092</t>
+  </si>
+  <si>
+    <t>iGrowan</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@iGrowan</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/growan.gg</t>
+  </si>
+  <si>
+    <t>GameMox</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@GameMoox</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hamedgamerr</t>
+  </si>
+  <si>
+    <t>Diyako News</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@DiyakoNewscodm</t>
+  </si>
+  <si>
+    <t>NOvEN</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@noven_yt</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/noven_yt?igsh=NjNieHVmbWdzOGl2</t>
+  </si>
+  <si>
+    <t>CoD Narco Live</t>
+  </si>
+  <si>
+    <t>codnarcoyt@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@codnarcolive</t>
+  </si>
+  <si>
+    <t>BOOM YT</t>
+  </si>
+  <si>
+    <t>boomytofficial@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@BoomTheGrinder</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/realboom90/</t>
+  </si>
+  <si>
+    <t>ParkerTheSlayer</t>
+  </si>
+  <si>
+    <t>parkertheslayer@amplifiedim.com</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@ParkerTheSlayerClips</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/realparkertheslayer/</t>
+  </si>
+  <si>
+    <t>Bobby Plays</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@BobbyPlays</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/bobbyplaysofficial</t>
+  </si>
+  <si>
+    <t>Ganyth</t>
+  </si>
+  <si>
+    <t>ganyth@amplifiedim.com</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@GanythYT</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/gxnyth</t>
+  </si>
+  <si>
+    <t>iFerg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@iFerg</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ifergyt/</t>
+  </si>
+  <si>
+    <t>Call of Duty: Mobile</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@callofdutymobile</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/callofdutymobile/</t>
+  </si>
+  <si>
+    <t>SPECBORG</t>
+  </si>
+  <si>
+    <t>specborgop@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@SPECBORG</t>
+  </si>
+  <si>
+    <t>SIFAT BS</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@SifatBs-w4z</t>
+  </si>
+  <si>
+    <t>Dozzy</t>
+  </si>
+  <si>
+    <t>dozzy@amplifiedim.com</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@Dozzylol</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/dozzylol/</t>
+  </si>
+  <si>
+    <t>Stealth CODM</t>
+  </si>
+  <si>
+    <t>megh62026@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/@StealthCODM</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/ig_stealthcodm/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FF1F2937"/>
+      <family val="2"/>
       <sz val="10"/>
-      <color rgb="FF1F2937"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
+      <color theme="10"/>
       <sz val="11"/>
-      <color theme="10"/>
       <name val="Carlito"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1089,9 +1283,8 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1143,10 +1336,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1356,9 +1548,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F103"/>
-  <sheetFormatPr defaultRowHeight="13.8" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F124"/>
+  <sheetFormatPr defaultRowHeight="13.8" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -1367,7 +1559,7 @@
     <col min="6" max="6" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" customHeight="1">
+    <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1387,7 +1579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.4" customHeight="1">
+    <row r="2" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -1403,7 +1595,7 @@
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
     </row>
-    <row r="3" spans="1:6" ht="14.4" customHeight="1">
+    <row r="3" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>10</v>
       </c>
@@ -1417,7 +1609,7 @@
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
     </row>
-    <row r="4" spans="1:6" ht="14.4" customHeight="1">
+    <row r="4" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -1431,7 +1623,7 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="1:6" ht="14.4" customHeight="1">
+    <row r="5" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>16</v>
       </c>
@@ -1443,7 +1635,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
     </row>
-    <row r="6" spans="1:6" ht="28.2" customHeight="1">
+    <row r="6" ht="28.2" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>18</v>
       </c>
@@ -1455,7 +1647,7 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
     </row>
-    <row r="7" spans="1:6" ht="14.4" customHeight="1">
+    <row r="7" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>20</v>
       </c>
@@ -1467,7 +1659,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="1:6" ht="14.4" customHeight="1">
+    <row r="8" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
@@ -1481,7 +1673,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
     </row>
-    <row r="9" spans="1:6" ht="14.4" customHeight="1">
+    <row r="9" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>25</v>
       </c>
@@ -1493,7 +1685,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="1:6" ht="14.4" customHeight="1">
+    <row r="10" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>27</v>
       </c>
@@ -1507,7 +1699,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
     </row>
-    <row r="11" spans="1:6" ht="14.4" customHeight="1">
+    <row r="11" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>30</v>
       </c>
@@ -1523,7 +1715,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="1:6" ht="14.4" customHeight="1">
+    <row r="12" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>34</v>
       </c>
@@ -1535,7 +1727,7 @@
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="1:6" ht="14.4" customHeight="1">
+    <row r="13" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>36</v>
       </c>
@@ -1547,7 +1739,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="1:6" ht="14.4" customHeight="1">
+    <row r="14" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>38</v>
       </c>
@@ -1559,7 +1751,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
     </row>
-    <row r="15" spans="1:6" ht="14.4" customHeight="1">
+    <row r="15" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>40</v>
       </c>
@@ -1573,7 +1765,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="1:6" ht="14.4" customHeight="1">
+    <row r="16" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>43</v>
       </c>
@@ -1589,7 +1781,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
     </row>
-    <row r="17" spans="1:6" ht="14.4" customHeight="1">
+    <row r="17" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>47</v>
       </c>
@@ -1601,7 +1793,7 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="1:6" ht="14.4" customHeight="1">
+    <row r="18" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>49</v>
       </c>
@@ -1615,7 +1807,7 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="1:6" ht="14.4" customHeight="1">
+    <row r="19" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>52</v>
       </c>
@@ -1629,7 +1821,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" ht="14.4" customHeight="1">
+    <row r="20" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>55</v>
       </c>
@@ -1641,7 +1833,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
     </row>
-    <row r="21" spans="1:6" ht="28.2" customHeight="1">
+    <row r="21" ht="28.2" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>57</v>
       </c>
@@ -1657,7 +1849,7 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
     </row>
-    <row r="22" spans="1:6" ht="14.4" customHeight="1">
+    <row r="22" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>61</v>
       </c>
@@ -1669,7 +1861,7 @@
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="1:6" ht="14.4" customHeight="1">
+    <row r="23" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>63</v>
       </c>
@@ -1683,7 +1875,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" ht="14.4" customHeight="1">
+    <row r="24" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>66</v>
       </c>
@@ -1699,7 +1891,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="1:6" ht="14.4" customHeight="1">
+    <row r="25" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>70</v>
       </c>
@@ -1713,7 +1905,7 @@
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="1:6" ht="14.4" customHeight="1">
+    <row r="26" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>73</v>
       </c>
@@ -1729,7 +1921,7 @@
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:6" ht="14.4" customHeight="1">
+    <row r="27" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>77</v>
       </c>
@@ -1743,7 +1935,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="1:6" ht="14.4" customHeight="1">
+    <row r="28" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>80</v>
       </c>
@@ -1759,7 +1951,7 @@
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="1:6" ht="28.2" customHeight="1">
+    <row r="29" ht="28.2" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>84</v>
       </c>
@@ -1775,7 +1967,7 @@
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
     </row>
-    <row r="30" spans="1:6" ht="14.4" customHeight="1">
+    <row r="30" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>88</v>
       </c>
@@ -1789,7 +1981,7 @@
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="1:6" ht="14.4" customHeight="1">
+    <row r="31" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>91</v>
       </c>
@@ -1801,7 +1993,7 @@
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="1:6" ht="14.4" customHeight="1">
+    <row r="32" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>93</v>
       </c>
@@ -1813,7 +2005,7 @@
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="1:6" ht="14.4" customHeight="1">
+    <row r="33" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>95</v>
       </c>
@@ -1825,7 +2017,7 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="1:6" ht="14.4" customHeight="1">
+    <row r="34" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>97</v>
       </c>
@@ -1839,7 +2031,7 @@
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="1:6" ht="14.4" customHeight="1">
+    <row r="35" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>100</v>
       </c>
@@ -1853,7 +2045,7 @@
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="1:6" ht="14.4" customHeight="1">
+    <row r="36" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>103</v>
       </c>
@@ -1867,7 +2059,7 @@
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
     </row>
-    <row r="37" spans="1:6" ht="14.4" customHeight="1">
+    <row r="37" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>106</v>
       </c>
@@ -1881,7 +2073,7 @@
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="1:6" ht="14.4" customHeight="1">
+    <row r="38" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>109</v>
       </c>
@@ -1893,7 +2085,7 @@
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
     </row>
-    <row r="39" spans="1:6" ht="14.4" customHeight="1">
+    <row r="39" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>111</v>
       </c>
@@ -1907,7 +2099,7 @@
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
     </row>
-    <row r="40" spans="1:6" ht="14.4" customHeight="1">
+    <row r="40" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>114</v>
       </c>
@@ -1919,7 +2111,7 @@
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
     </row>
-    <row r="41" spans="1:6" ht="14.4" customHeight="1">
+    <row r="41" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>116</v>
       </c>
@@ -1933,7 +2125,7 @@
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
     </row>
-    <row r="42" spans="1:6" ht="14.4" customHeight="1">
+    <row r="42" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>119</v>
       </c>
@@ -1945,7 +2137,7 @@
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
     </row>
-    <row r="43" spans="1:6" ht="14.4" customHeight="1">
+    <row r="43" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>121</v>
       </c>
@@ -1957,7 +2149,7 @@
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
     </row>
-    <row r="44" spans="1:6" ht="14.4" customHeight="1">
+    <row r="44" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>123</v>
       </c>
@@ -1971,7 +2163,7 @@
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
     </row>
-    <row r="45" spans="1:6" ht="14.4" customHeight="1">
+    <row r="45" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>126</v>
       </c>
@@ -1985,7 +2177,7 @@
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
     </row>
-    <row r="46" spans="1:6" ht="14.4" customHeight="1">
+    <row r="46" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>129</v>
       </c>
@@ -1997,7 +2189,7 @@
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
     </row>
-    <row r="47" spans="1:6" ht="14.4" customHeight="1">
+    <row r="47" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>131</v>
       </c>
@@ -2013,7 +2205,7 @@
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
     </row>
-    <row r="48" spans="1:6" ht="14.4" customHeight="1">
+    <row r="48" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>135</v>
       </c>
@@ -2027,7 +2219,7 @@
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
     </row>
-    <row r="49" spans="1:6" ht="14.4" customHeight="1">
+    <row r="49" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>138</v>
       </c>
@@ -2041,7 +2233,7 @@
       <c r="E49" s="7"/>
       <c r="F49" s="7"/>
     </row>
-    <row r="50" spans="1:6" ht="14.4" customHeight="1">
+    <row r="50" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>141</v>
       </c>
@@ -2057,7 +2249,7 @@
       <c r="E50" s="7"/>
       <c r="F50" s="7"/>
     </row>
-    <row r="51" spans="1:6" ht="14.4" customHeight="1">
+    <row r="51" ht="14.4" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>145</v>
       </c>
@@ -2071,7 +2263,7 @@
       </c>
       <c r="F51" s="7"/>
     </row>
-    <row r="52" spans="1:6" ht="14.4" customHeight="1">
+    <row r="52" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>148</v>
       </c>
@@ -2085,7 +2277,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="14.4" customHeight="1">
+    <row r="53" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>151</v>
       </c>
@@ -2096,7 +2288,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="14.4">
+    <row r="54" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>154</v>
       </c>
@@ -2110,7 +2302,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="14.4">
+    <row r="55" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>158</v>
       </c>
@@ -2124,7 +2316,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="14.4">
+    <row r="56" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>162</v>
       </c>
@@ -2135,7 +2327,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="14.4">
+    <row r="57" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>165</v>
       </c>
@@ -2143,7 +2335,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="14.4">
+    <row r="58" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>167</v>
       </c>
@@ -2157,7 +2349,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="14.4">
+    <row r="59" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>171</v>
       </c>
@@ -2171,7 +2363,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="14.4">
+    <row r="60" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>175</v>
       </c>
@@ -2185,7 +2377,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="14.4">
+    <row r="61" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>179</v>
       </c>
@@ -2196,7 +2388,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="14.4">
+    <row r="62" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>182</v>
       </c>
@@ -2207,7 +2399,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="14.4">
+    <row r="63" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>185</v>
       </c>
@@ -2218,7 +2410,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="14.4">
+    <row r="64" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>188</v>
       </c>
@@ -2229,7 +2421,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="14.4">
+    <row r="65" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>191</v>
       </c>
@@ -2240,7 +2432,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="14.4">
+    <row r="66" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>194</v>
       </c>
@@ -2251,7 +2443,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="14.4">
+    <row r="67" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>197</v>
       </c>
@@ -2262,7 +2454,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="14.4">
+    <row r="68" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>200</v>
       </c>
@@ -2273,7 +2465,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="14.4">
+    <row r="69" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>203</v>
       </c>
@@ -2287,7 +2479,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="14.4">
+    <row r="70" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>207</v>
       </c>
@@ -2298,7 +2490,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="14.4">
+    <row r="71" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>210</v>
       </c>
@@ -2309,7 +2501,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="14.4">
+    <row r="72" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>213</v>
       </c>
@@ -2323,7 +2515,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="14.4">
+    <row r="73" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>217</v>
       </c>
@@ -2337,7 +2529,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="14.4">
+    <row r="74" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>221</v>
       </c>
@@ -2345,7 +2537,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="14.4">
+    <row r="75" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>223</v>
       </c>
@@ -2359,7 +2551,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="14.4">
+    <row r="76" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>227</v>
       </c>
@@ -2367,7 +2559,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="14.4">
+    <row r="77" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>229</v>
       </c>
@@ -2378,7 +2570,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="14.4">
+    <row r="78" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>232</v>
       </c>
@@ -2392,7 +2584,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="14.4">
+    <row r="79" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>236</v>
       </c>
@@ -2403,7 +2595,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="14.4">
+    <row r="80" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>239</v>
       </c>
@@ -2411,7 +2603,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="14.4">
+    <row r="81" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>241</v>
       </c>
@@ -2422,7 +2614,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="14.4">
+    <row r="82" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>244</v>
       </c>
@@ -2433,7 +2625,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="14.4">
+    <row r="83" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>247</v>
       </c>
@@ -2441,7 +2633,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="14.4">
+    <row r="84" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>249</v>
       </c>
@@ -2449,7 +2641,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="85" spans="1:4" ht="14.4">
+    <row r="85" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>251</v>
       </c>
@@ -2457,7 +2649,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="14.4">
+    <row r="86" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>253</v>
       </c>
@@ -2465,7 +2657,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="14.4">
+    <row r="87" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>255</v>
       </c>
@@ -2476,7 +2668,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="14.4">
+    <row r="88" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>258</v>
       </c>
@@ -2487,7 +2679,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="14.4">
+    <row r="89" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>261</v>
       </c>
@@ -2498,7 +2690,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="14.4">
+    <row r="90" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>264</v>
       </c>
@@ -2509,7 +2701,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="14.4">
+    <row r="91" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>267</v>
       </c>
@@ -2523,7 +2715,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="14.4">
+    <row r="92" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>271</v>
       </c>
@@ -2534,7 +2726,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="93" spans="1:4" ht="14.4">
+    <row r="93" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>274</v>
       </c>
@@ -2545,7 +2737,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="14.4">
+    <row r="94" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>277</v>
       </c>
@@ -2556,7 +2748,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="14.4">
+    <row r="95" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>280</v>
       </c>
@@ -2564,7 +2756,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="14.4">
+    <row r="96" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>282</v>
       </c>
@@ -2572,7 +2764,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="14.4">
+    <row r="97" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>284</v>
       </c>
@@ -2586,7 +2778,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="14.4">
+    <row r="98" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>288</v>
       </c>
@@ -2597,7 +2789,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="14.4">
+    <row r="99" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>291</v>
       </c>
@@ -2608,7 +2800,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="14.4">
+    <row r="100" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>294</v>
       </c>
@@ -2619,7 +2811,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="14.4">
+    <row r="101" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>297</v>
       </c>
@@ -2627,7 +2819,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="14.4">
+    <row r="102" ht="14.4" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>299</v>
       </c>
@@ -2635,7 +2827,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="14.4">
+    <row r="103" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>301</v>
       </c>
@@ -2649,82 +2841,319 @@
         <v>304</v>
       </c>
     </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>305</v>
+      </c>
+      <c r="C104" t="s">
+        <v>306</v>
+      </c>
+      <c r="D104" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>308</v>
+      </c>
+      <c r="B105" t="s">
+        <v>309</v>
+      </c>
+      <c r="C105" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>311</v>
+      </c>
+      <c r="B106" t="s">
+        <v>312</v>
+      </c>
+      <c r="C106" t="s">
+        <v>313</v>
+      </c>
+      <c r="D106" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>315</v>
+      </c>
+      <c r="C107" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>317</v>
+      </c>
+      <c r="C108" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>319</v>
+      </c>
+      <c r="B109" t="s">
+        <v>320</v>
+      </c>
+      <c r="C109" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>322</v>
+      </c>
+      <c r="C110" t="s">
+        <v>323</v>
+      </c>
+      <c r="D110" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>325</v>
+      </c>
+      <c r="C111" t="s">
+        <v>326</v>
+      </c>
+      <c r="D111" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>328</v>
+      </c>
+      <c r="C112" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>330</v>
+      </c>
+      <c r="C113" t="s">
+        <v>331</v>
+      </c>
+      <c r="D113" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>333</v>
+      </c>
+      <c r="B114" t="s">
+        <v>334</v>
+      </c>
+      <c r="C114" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>336</v>
+      </c>
+      <c r="B115" t="s">
+        <v>337</v>
+      </c>
+      <c r="C115" t="s">
+        <v>338</v>
+      </c>
+      <c r="D115" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>340</v>
+      </c>
+      <c r="B116" t="s">
+        <v>341</v>
+      </c>
+      <c r="C116" t="s">
+        <v>342</v>
+      </c>
+      <c r="D116" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>344</v>
+      </c>
+      <c r="C117" t="s">
+        <v>345</v>
+      </c>
+      <c r="D117" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>347</v>
+      </c>
+      <c r="B118" t="s">
+        <v>348</v>
+      </c>
+      <c r="C118" t="s">
+        <v>349</v>
+      </c>
+      <c r="D118" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>351</v>
+      </c>
+      <c r="C119" t="s">
+        <v>352</v>
+      </c>
+      <c r="D119" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>354</v>
+      </c>
+      <c r="C120" t="s">
+        <v>355</v>
+      </c>
+      <c r="D120" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>357</v>
+      </c>
+      <c r="B121" t="s">
+        <v>358</v>
+      </c>
+      <c r="C121" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>360</v>
+      </c>
+      <c r="C122" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>362</v>
+      </c>
+      <c r="B123" t="s">
+        <v>363</v>
+      </c>
+      <c r="C123" t="s">
+        <v>364</v>
+      </c>
+      <c r="D123" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>366</v>
+      </c>
+      <c r="B124" t="s">
+        <v>367</v>
+      </c>
+      <c r="C124" t="s">
+        <v>368</v>
+      </c>
+      <c r="D124" t="s">
+        <v>369</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="D2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C4" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="C6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="C7" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="C8" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="C9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="C10" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="D10" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="C11" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="D11" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="C12" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="C13" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="C14" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="C15" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="C16" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="D16" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="C17" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="C18" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="C19" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="D19" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="C20" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="C21" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="D21" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="C22" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="C23" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="C24" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="D24" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="C25" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="C26" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="D26" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="C27" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="D27" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="C28" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="D28" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="C29" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="D29" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="C30" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="C31" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="C32" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="C33" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="C34" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="D34" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="C35" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="D35" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="C36" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="D36" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="C37" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="C38" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="C39" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="D39" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="C40" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="C41" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="C42" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="C43" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="C44" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="D44" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="C45" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="C46" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="C47" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="D47" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="C48" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="C49" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="D49" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="C50" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="D50" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="C51" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="C52" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="C53" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="C59" r:id="rId72" xr:uid="{74383771-B7B9-46D6-9A52-FD2392D61376}"/>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="D2" r:id="rId2"/>
+    <hyperlink ref="C3" r:id="rId3"/>
+    <hyperlink ref="C4" r:id="rId4"/>
+    <hyperlink ref="C5" r:id="rId5"/>
+    <hyperlink ref="C6" r:id="rId6"/>
+    <hyperlink ref="C7" r:id="rId7"/>
+    <hyperlink ref="C8" r:id="rId8"/>
+    <hyperlink ref="C9" r:id="rId9"/>
+    <hyperlink ref="C10" r:id="rId10"/>
+    <hyperlink ref="D10" r:id="rId11"/>
+    <hyperlink ref="C11" r:id="rId12"/>
+    <hyperlink ref="D11" r:id="rId13"/>
+    <hyperlink ref="C12" r:id="rId14"/>
+    <hyperlink ref="C13" r:id="rId15"/>
+    <hyperlink ref="C14" r:id="rId16"/>
+    <hyperlink ref="C15" r:id="rId17"/>
+    <hyperlink ref="C16" r:id="rId18"/>
+    <hyperlink ref="D16" r:id="rId19"/>
+    <hyperlink ref="C17" r:id="rId20"/>
+    <hyperlink ref="C18" r:id="rId21"/>
+    <hyperlink ref="C19" r:id="rId22"/>
+    <hyperlink ref="D19" r:id="rId23"/>
+    <hyperlink ref="C20" r:id="rId24"/>
+    <hyperlink ref="C21" r:id="rId25"/>
+    <hyperlink ref="D21" r:id="rId26"/>
+    <hyperlink ref="C22" r:id="rId27"/>
+    <hyperlink ref="C23" r:id="rId28"/>
+    <hyperlink ref="C24" r:id="rId29"/>
+    <hyperlink ref="D24" r:id="rId30"/>
+    <hyperlink ref="C25" r:id="rId31"/>
+    <hyperlink ref="C26" r:id="rId32"/>
+    <hyperlink ref="D26" r:id="rId33"/>
+    <hyperlink ref="C27" r:id="rId34"/>
+    <hyperlink ref="D27" r:id="rId35"/>
+    <hyperlink ref="C28" r:id="rId36"/>
+    <hyperlink ref="D28" r:id="rId37"/>
+    <hyperlink ref="C29" r:id="rId38"/>
+    <hyperlink ref="D29" r:id="rId39"/>
+    <hyperlink ref="C30" r:id="rId40"/>
+    <hyperlink ref="C31" r:id="rId41"/>
+    <hyperlink ref="C32" r:id="rId42"/>
+    <hyperlink ref="C33" r:id="rId43"/>
+    <hyperlink ref="C34" r:id="rId44"/>
+    <hyperlink ref="D34" r:id="rId45"/>
+    <hyperlink ref="C35" r:id="rId46"/>
+    <hyperlink ref="D35" r:id="rId47"/>
+    <hyperlink ref="C36" r:id="rId48"/>
+    <hyperlink ref="D36" r:id="rId49"/>
+    <hyperlink ref="C37" r:id="rId50"/>
+    <hyperlink ref="C38" r:id="rId51"/>
+    <hyperlink ref="C39" r:id="rId52"/>
+    <hyperlink ref="D39" r:id="rId53"/>
+    <hyperlink ref="C40" r:id="rId54"/>
+    <hyperlink ref="C41" r:id="rId55"/>
+    <hyperlink ref="C42" r:id="rId56"/>
+    <hyperlink ref="C43" r:id="rId57"/>
+    <hyperlink ref="C44" r:id="rId58"/>
+    <hyperlink ref="D44" r:id="rId59"/>
+    <hyperlink ref="C45" r:id="rId60"/>
+    <hyperlink ref="C46" r:id="rId61"/>
+    <hyperlink ref="C47" r:id="rId62"/>
+    <hyperlink ref="D47" r:id="rId63"/>
+    <hyperlink ref="C48" r:id="rId64"/>
+    <hyperlink ref="C49" r:id="rId65"/>
+    <hyperlink ref="D49" r:id="rId66"/>
+    <hyperlink ref="C50" r:id="rId67"/>
+    <hyperlink ref="D50" r:id="rId68"/>
+    <hyperlink ref="C51" r:id="rId69"/>
+    <hyperlink ref="C52" r:id="rId70"/>
+    <hyperlink ref="C53" r:id="rId71"/>
+    <hyperlink ref="C59" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>